--- a/3_Test_Cases/Test_Cases.xlsx
+++ b/3_Test_Cases/Test_Cases.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9302"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="4" rupBuild="9303"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="110" windowWidth="14810" windowHeight="8010"/>
@@ -16,10 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="110">
-  <si>
-    <t>PROJECT NAME</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="113">
   <si>
     <t>E-COMMERCE WEBSITE</t>
   </si>
@@ -27,9 +24,6 @@
     <t>MODULE</t>
   </si>
   <si>
-    <t>QA</t>
-  </si>
-  <si>
     <t>MEHTAB ALI</t>
   </si>
   <si>
@@ -346,13 +340,28 @@
   </si>
   <si>
     <t>Add product , Checkout , Enter details</t>
+  </si>
+  <si>
+    <t>28/03/2026</t>
+  </si>
+  <si>
+    <t>PROJECT NAME:</t>
+  </si>
+  <si>
+    <t>DATE:</t>
+  </si>
+  <si>
+    <t>QA:</t>
+  </si>
+  <si>
+    <t>TEST CASE FOR E-COMMERCE WEBSITE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -376,8 +385,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Algerian"/>
+      <family val="5"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Algerian"/>
+      <family val="5"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <u val="double"/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Arial Rounded MT Bold"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -414,6 +461,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -427,37 +492,62 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -762,669 +852,681 @@
   <dimension ref="A1:G51"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="10.7265625" customWidth="1"/>
-    <col min="3" max="3" width="19.36328125" customWidth="1"/>
-    <col min="4" max="4" width="45.1796875" customWidth="1"/>
-    <col min="5" max="5" width="29.90625" customWidth="1"/>
-    <col min="6" max="6" width="17.1796875" customWidth="1"/>
+    <col min="1" max="1" width="10" style="4" customWidth="1"/>
+    <col min="2" max="2" width="10.7265625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="22" style="4" customWidth="1"/>
+    <col min="4" max="4" width="46" style="4" customWidth="1"/>
+    <col min="5" max="5" width="34.7265625" style="4" customWidth="1"/>
+    <col min="6" max="6" width="17.1796875" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.7265625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="E1" s="2"/>
+    <row r="1" spans="1:7" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="C1" s="17"/>
+      <c r="D1" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E1" s="18"/>
     </row>
     <row r="3" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="E3" s="13" t="s">
+    </row>
+    <row r="4" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="D4" s="8" t="s">
+        <v>110</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
+      <c r="D5" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" s="9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+    </row>
+    <row r="8" spans="1:7" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="C8" s="11" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="D5" s="13" t="s">
+      <c r="D8" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="B9" s="2" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="G6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-    </row>
-    <row r="8" spans="1:7" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A8" s="3"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="11" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" s="10" t="s">
+      <c r="C9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="G10" s="5"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="C17" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D17" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="C25" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A27" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A28" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C29" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="19.5" x14ac:dyDescent="0.4">
+      <c r="C32" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A34" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="F34" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A35" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>71</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A36" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="F36" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="C38" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A39" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A40" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D40" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="5" t="s">
+      <c r="E40" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="F40" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A41" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A42" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="19.5" x14ac:dyDescent="0.35">
+      <c r="C44" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C45" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="D45" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="E45" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="F45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="4" t="s">
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A46" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A47" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="F47" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="19.5" x14ac:dyDescent="0.45">
+      <c r="C49" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A51" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F51" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="1"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="C17" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D17" s="6" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C18" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E18" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F20" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F22" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="C25" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E28" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F28" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="C32" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D32" s="12" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F33" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="D34" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="E35" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="F35" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D36" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="E36" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="F36" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="C38" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B39" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C39" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F39" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="E42" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="F42" s="4" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="C44" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B45" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C45" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D45" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F45" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E46" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="F46" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="E47" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="F47" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="18.5" x14ac:dyDescent="0.45">
-      <c r="C49" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B50" s="8" t="s">
-        <v>6</v>
-      </c>
-      <c r="C50" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="D50" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="F50" s="8" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="F51" s="4" t="s">
-        <v>15</v>
-      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D1:E1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
